--- a/spreadsheet/macrofree/waf_checklist.en.xlsx
+++ b/spreadsheet/macrofree/waf_checklist.en.xlsx
@@ -1128,7 +1128,11 @@
         </is>
       </c>
       <c r="J11" s="13" t="n"/>
-      <c r="K11" s="19" t="n"/>
+      <c r="K11" s="19" t="inlineStr">
+        <is>
+          <t>resources | where type =~ 'Microsoft.ContainerRegistry/registries' | extend acrName = name, acrId = id | extend encryptionStatus = properties.encryption.status  | extend compliant = iif(encryptionStatus == 'disabled', false, true) | project acrName, acrId, encryptionStatus, compliant</t>
+        </is>
+      </c>
       <c r="L11" s="19" t="inlineStr">
         <is>
           <t>0bd05dc2-efd5-4d76-8d41-d2500cc47b49</t>
@@ -1238,7 +1242,11 @@
         </is>
       </c>
       <c r="J13" s="13" t="n"/>
-      <c r="K13" s="19" t="n"/>
+      <c r="K13" s="19" t="inlineStr">
+        <is>
+          <t>resources | where type =~ 'microsoft.containerregistry/registries' | extend localAdminDisabled = properties.adminUserEnabled // Adjust this property as needed | extend compliant = iif(localAdminDisabled == 'false', true, false) // Check if local admin is disabled | project compliant, name, id, tags | distinct id, compliant</t>
+        </is>
+      </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
           <t>be0e38ce-e297-411b-b363-caaab79b198d</t>
@@ -1293,7 +1301,11 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="19" t="n"/>
+      <c r="K14" s="19" t="inlineStr">
+        <is>
+          <t>resources | where type =~ 'microsoft.containerregistry/registries' | extend localAdminDisabled = properties.adminUserEnabled // Adjust this property as needed | extend compliant = iif(localAdminDisabled == 'false', true, false) // Check if local admin is disabled | project compliant, name, id, tags | distinct id, compliant</t>
+        </is>
+      </c>
       <c r="L14" s="19" t="inlineStr">
         <is>
           <t>387e5ced-126c-4d13-8af5-b20c6998a646</t>
@@ -1348,7 +1360,11 @@
         </is>
       </c>
       <c r="J15" s="13" t="n"/>
-      <c r="K15" s="19" t="n"/>
+      <c r="K15" s="19" t="inlineStr">
+        <is>
+          <t>resources | where type =~ 'microsoft.containerregistry/registries' | extend compliant = iif(properties.anonymousPullEnabled == false, true, false) | project compliant, name, id, tags | distinct id, compliant</t>
+        </is>
+      </c>
       <c r="L15" s="19" t="inlineStr">
         <is>
           <t>e338997e-41c7-47d7-acf6-a62a1194956d</t>
@@ -1674,7 +1690,11 @@
         </is>
       </c>
       <c r="J21" s="13" t="n"/>
-      <c r="K21" s="19" t="n"/>
+      <c r="K21" s="19" t="inlineStr">
+        <is>
+          <t>resources | where type =~ 'Microsoft.ContainerRegistry/registries' | where sku.name =~ 'Premium' // Check for Premium SKU | extend publicAccessEnabled = properties.publicNetworkAccess | extend defaultAction = tostring(properties.networkRuleSet.defaultAction) // Extract defaultAction | extend compliant = iif(publicAccessEnabled != 'Enabled' or defaultAction == 'Deny', true, false) | project name, id, publicAccessEnabled, defaultAction, compliant</t>
+        </is>
+      </c>
       <c r="L21" s="19" t="inlineStr">
         <is>
           <t>cd289ced-6b17-4db8-8554-62f2aee4553a</t>
@@ -1729,7 +1749,11 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="19" t="n"/>
+      <c r="K22" s="19" t="inlineStr">
+        <is>
+          <t>resources | where type =~ 'Microsoft.ContainerRegistry/registries' | extend skuName = sku.name // Extract the SKU name | extend compliant = iif(skuName == 'Premium', true, false) // Check if SKU is Premium | project name, id, skuName, compliant</t>
+        </is>
+      </c>
       <c r="L22" s="19" t="inlineStr">
         <is>
           <t>fc833934-8b26-42d6-ac5f-512925498f6d</t>
@@ -56757,7 +56781,11 @@
         </is>
       </c>
       <c r="J1066" s="13" t="n"/>
-      <c r="K1066" s="19" t="n"/>
+      <c r="K1066" s="19" t="inlineStr">
+        <is>
+          <t>resources | where type =~ 'microsoft.network/frontdoorwebapplicationfirewallpolicies' | project policyName=name, policyId=id,policySku=sku.name, links=properties.securityPolicyLinks, enabledState=properties.policySettings.enabledState, mode=properties.policySettings.mode | mvexpand links | extend securityPolicy=links.id | extend securityPolicyParts=split(securityPolicy, '/') | extend profileId=strcat_array(array_slice(securityPolicyParts, 0, -3), '/') | project id=profileId, compliant=((enabledState=~'Enabled') and (mode=~'Prevention')), enabledState, mode</t>
+        </is>
+      </c>
       <c r="L1066" s="19" t="inlineStr">
         <is>
           <t>28b9ee82-b2c7-45aa-bc98-6de6f59a095d</t>
